--- a/Excel/FurnitureConfig.xlsx
+++ b/Excel/FurnitureConfig.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>基础餐桌</t>
+          <t>木纹小餐桌</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -485,15 +485,105 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>木质柜台</t>
+          <t>温暖木柜台</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
+        <is>
+          <t>furniture_shelf_ingredient</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>食材展示架</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>furniture_lamp_firefly</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>萤火灯笼</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>furniture_wall_map</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>迷宫手绘地图</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>furniture_stove_copper</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>铜锅炉灶</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>furniture_flower_corner</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>香草盆栽角</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>furniture_vip_table</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>丰收长桌</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>END</t>
         </is>
